--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="203">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -295,21 +295,48 @@
     <t>fr-lm-allergy-intolerance.header.author[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur</t>
-  </si>
-  <si>
-    <t>Auteur(s) responsable(s) : Personne(s) ayant la responsabilité des informations fournies. Le rôle précis de l’auteur responsable dépend du contexte d’usage et du modèle concerné.</t>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
   </si>
   <si>
     <t>fr-lm-entry.header.author[x]</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.header.performer</t>
+    <t>fr-lm-allergy-intolerance.header.author[x].authorProfessional</t>
   </si>
   <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -924,11 +951,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ37"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41.06640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.61328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="49.61328125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1502,13 +1529,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>93</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1559,7 +1586,7 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
@@ -1576,10 +1603,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1602,13 +1629,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>97</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1659,7 +1686,7 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
@@ -1676,10 +1703,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1702,13 +1729,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1759,7 +1786,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1776,10 +1803,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1802,13 +1829,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1859,7 +1886,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1876,10 +1903,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1890,7 +1917,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1902,13 +1929,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,13 +1986,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1976,10 +2003,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1990,7 +2017,7 @@
         <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -2002,13 +2029,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2059,13 +2086,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -2076,10 +2103,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2090,7 +2117,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -2102,13 +2129,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2159,13 +2186,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -2176,10 +2203,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2187,7 +2214,7 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
         <v>79</v>
@@ -2202,13 +2229,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2238,10 +2265,10 @@
         <v>73</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>73</v>
@@ -2259,10 +2286,10 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
         <v>79</v>
@@ -2276,10 +2303,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2287,7 +2314,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>79</v>
@@ -2302,13 +2329,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2359,10 +2386,10 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>79</v>
@@ -2387,7 +2414,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>79</v>
@@ -2402,7 +2429,7 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s" s="2">
         <v>125</v>
@@ -2459,10 +2486,10 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>79</v>
@@ -2476,10 +2503,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2487,7 +2514,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2502,7 +2529,7 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>128</v>
@@ -2538,10 +2565,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2559,10 +2586,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2576,10 +2603,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2587,7 +2614,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2602,13 +2629,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2638,31 +2665,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>131</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>129</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2687,7 +2714,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2702,7 +2729,7 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>134</v>
@@ -2738,10 +2765,10 @@
         <v>73</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>73</v>
@@ -2762,7 +2789,7 @@
         <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2776,10 +2803,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2802,13 +2829,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2838,10 +2865,10 @@
         <v>73</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>139</v>
+        <v>73</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>73</v>
@@ -2859,7 +2886,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2876,10 +2903,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2887,7 +2914,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2902,13 +2929,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2938,10 +2965,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2959,10 +2986,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2971,15 +2998,15 @@
         <v>73</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3002,13 +3029,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3038,10 +3065,10 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>73</v>
+        <v>144</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3059,7 +3086,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3076,21 +3103,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>73</v>
@@ -3102,17 +3129,15 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>73</v>
@@ -3140,48 +3165,48 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>73</v>
+        <v>148</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3204,17 +3229,15 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>73</v>
@@ -3263,7 +3286,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3275,15 +3298,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3306,13 +3329,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3363,7 +3386,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3375,26 +3398,26 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3406,15 +3429,17 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3451,39 +3476,39 @@
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3491,7 +3516,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3506,15 +3531,17 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
@@ -3566,7 +3593,7 @@
         <v>173</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3580,10 +3607,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3594,7 +3621,7 @@
         <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>73</v>
@@ -3606,13 +3633,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>176</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3663,27 +3690,27 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3706,13 +3733,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3742,7 +3769,7 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="Z28" t="s" s="2">
         <v>73</v>
@@ -3763,7 +3790,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3780,10 +3807,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3791,7 +3818,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>
@@ -3806,13 +3833,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3842,31 +3869,31 @@
         <v>73</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="Z29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>180</v>
-      </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -3880,10 +3907,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3894,7 +3921,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3906,13 +3933,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3942,10 +3969,10 @@
         <v>73</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>185</v>
+        <v>73</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>73</v>
@@ -3963,13 +3990,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -3980,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3991,7 +4018,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>79</v>
@@ -4006,13 +4033,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4042,7 +4069,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>188</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4063,10 +4090,10 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>79</v>
@@ -4075,15 +4102,15 @@
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4091,7 +4118,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4106,13 +4133,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>147</v>
+        <v>190</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4142,7 +4169,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4163,10 +4190,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4180,21 +4207,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4206,17 +4233,15 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>73</v>
@@ -4244,48 +4269,48 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>73</v>
+        <v>195</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>144</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4308,17 +4333,15 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>73</v>
@@ -4367,7 +4390,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>164</v>
+        <v>196</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4379,15 +4402,15 @@
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4410,13 +4433,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4467,7 +4490,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4479,26 +4502,26 @@
         <v>73</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>170</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4510,15 +4533,17 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>108</v>
+        <v>160</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>162</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -4555,39 +4580,39 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4595,7 +4620,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>79</v>
@@ -4610,15 +4635,17 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
@@ -4667,10 +4694,10 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -4679,6 +4706,306 @@
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="206">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,6 +406,15 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.code</t>
+  </si>
+  <si>
+    <t>Type de l'entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.code</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.type</t>
@@ -951,7 +960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.61328125" customWidth="true" bestFit="true"/>
@@ -2514,7 +2523,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2565,31 +2574,31 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="Z16" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>127</v>
-      </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2603,10 +2612,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2632,10 +2641,10 @@
         <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2665,10 +2674,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>132</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2686,7 +2695,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2703,10 +2712,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2732,10 +2741,10 @@
         <v>121</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2786,7 +2795,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2803,10 +2812,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2814,7 +2823,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2829,7 +2838,7 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>137</v>
@@ -2886,10 +2895,10 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2929,13 +2938,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2965,10 +2974,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>141</v>
+        <v>73</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3003,10 +3012,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3032,10 +3041,10 @@
         <v>121</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3065,11 +3074,11 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="Z21" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
       </c>
@@ -3086,7 +3095,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3103,10 +3112,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3132,10 +3141,10 @@
         <v>121</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3165,11 +3174,11 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="Z22" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="Z22" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
       </c>
@@ -3186,7 +3195,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3203,10 +3212,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3214,7 +3223,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3229,13 +3238,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3265,10 +3274,10 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3286,10 +3295,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3298,15 +3307,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3314,7 +3323,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3329,13 +3338,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3386,10 +3395,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3398,26 +3407,26 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3429,17 +3438,15 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3476,50 +3483,50 @@
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3531,16 +3538,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3578,39 +3585,39 @@
         <v>73</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3618,7 +3625,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3633,15 +3640,17 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -3690,10 +3699,10 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3702,15 +3711,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3733,13 +3742,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3790,7 +3799,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3802,15 +3811,15 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3836,10 +3845,10 @@
         <v>117</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3890,7 +3899,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3907,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3921,7 +3930,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3933,13 +3942,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3990,13 +3999,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -4007,10 +4016,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4021,7 +4030,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4033,13 +4042,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4069,7 +4078,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4090,13 +4099,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4118,7 +4127,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4193,7 +4202,7 @@
         <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4218,7 +4227,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>79</v>
@@ -4272,7 +4281,7 @@
         <v>194</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>195</v>
+        <v>73</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4293,7 +4302,7 @@
         <v>192</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>79</v>
@@ -4307,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4318,7 +4327,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>79</v>
@@ -4333,13 +4342,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4369,10 +4378,10 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>73</v>
@@ -4390,10 +4399,10 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>79</v>
@@ -4402,15 +4411,15 @@
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4418,7 +4427,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -4433,13 +4442,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>155</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4490,10 +4499,10 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>157</v>
+        <v>199</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -4502,26 +4511,26 @@
         <v>73</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4533,17 +4542,15 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>163</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -4580,50 +4587,50 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>153</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
@@ -4635,16 +4642,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4682,39 +4689,39 @@
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>73</v>
+        <v>168</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4722,7 +4729,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>79</v>
@@ -4737,15 +4744,17 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L38" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>73</v>
@@ -4794,10 +4803,10 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>79</v>
@@ -4806,15 +4815,15 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>179</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4837,13 +4846,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4894,7 +4903,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4906,15 +4915,15 @@
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4940,10 +4949,10 @@
         <v>117</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4994,7 +5003,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5006,6 +5015,106 @@
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="204">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allergie ou hypersensibilite</t>
+    <t>Entrée Allergie ou Hypersensibilité</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -408,19 +408,10 @@
     <t>fr-lm-entry.header.langue</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
-  </si>
-  <si>
     <t>fr-lm-allergy-intolerance.type</t>
   </si>
   <si>
-    <t>Allergie / hypersensibilité non allergique / intolérance / idiosyncrasie : jdv-type-event-indesirable-previsible-cisis (1.2.250.1.213.1.1.5.842)</t>
+    <t>Allergie / hypersensibilité non allergique / intolérance / idiosyncrasie</t>
   </si>
   <si>
     <t xml:space="preserve"> jdv-type-event-indesirable-previsible-cisis (1.2.250.1.213.1.1.5.842)</t>
@@ -432,7 +423,10 @@
     <t>fr-lm-allergy-intolerance.category</t>
   </si>
   <si>
-    <t>food | medication | environment | biologic : jdv-hl7-allergy-intolerance-category-cisis (2.16.840.1.113883.4.642.3.133</t>
+    <t>food | medication | environment | biologic</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jdv-hl7-allergy-intolerance-category-cisis (2.16.840.1.113883.4.642.3.133)</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.agentOrAllergen</t>
@@ -459,8 +453,7 @@
     <t>fr-lm-allergy-intolerance.status</t>
   </si>
   <si>
-    <t>Statut clinique de l'allergie
-Description du binding: : jdv-hl7-allergyintolerance-clinical-cisis (2.16.840.1.113883.4.642.3.1372)</t>
+    <t>Statut clinique de l'allergie</t>
   </si>
   <si>
     <t>jdv-hl7-allergyintolerance-clinical-cisis (2.16.840.1.113883.4.642.3.1372)</t>
@@ -960,7 +953,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ41"/>
+  <dimension ref="A1:AJ40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.61328125" customWidth="true" bestFit="true"/>
@@ -987,7 +980,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="59.48828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="60.30078125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="69.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2523,7 +2516,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2574,10 +2567,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2595,10 +2588,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2612,10 +2605,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2641,10 +2634,10 @@
         <v>121</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2674,10 +2667,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>133</v>
+        <v>73</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2695,7 +2688,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2823,7 +2816,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>79</v>
@@ -2838,13 +2831,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2898,7 +2891,7 @@
         <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>79</v>
@@ -2912,10 +2905,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2938,7 +2931,7 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>140</v>
@@ -2974,10 +2967,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>73</v>
+        <v>141</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2995,7 +2988,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3012,10 +3005,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3041,10 +3034,10 @@
         <v>121</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3074,28 +3067,28 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3112,10 +3105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3141,10 +3134,10 @@
         <v>121</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3174,28 +3167,28 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3212,10 +3205,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3223,7 +3216,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3238,13 +3231,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3274,31 +3267,31 @@
         <v>73</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>152</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>149</v>
-      </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3307,15 +3300,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3323,7 +3316,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3338,13 +3331,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3395,10 +3388,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3407,26 +3400,26 @@
         <v>73</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3438,15 +3431,17 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3483,50 +3478,50 @@
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3538,16 +3533,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3585,39 +3580,39 @@
         <v>73</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3625,7 +3620,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3640,17 +3635,15 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>73</v>
@@ -3699,10 +3692,10 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3711,15 +3704,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3742,13 +3735,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3811,7 +3804,7 @@
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
@@ -3930,7 +3923,7 @@
         <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3942,7 +3935,7 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>186</v>
@@ -4005,7 +3998,7 @@
         <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -4030,7 +4023,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -4042,7 +4035,7 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>188</v>
@@ -4078,7 +4071,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4105,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4116,10 +4109,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4127,7 +4120,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4145,10 +4138,10 @@
         <v>121</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4178,7 +4171,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4199,10 +4192,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4216,10 +4209,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4227,7 +4220,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>79</v>
@@ -4245,10 +4238,10 @@
         <v>121</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4278,10 +4271,10 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4299,10 +4292,10 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>79</v>
@@ -4316,10 +4309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4327,7 +4320,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>79</v>
@@ -4342,13 +4335,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>196</v>
+        <v>153</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4378,31 +4371,31 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>195</v>
-      </c>
       <c r="AG34" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>79</v>
@@ -4411,15 +4404,15 @@
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4427,7 +4420,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -4442,13 +4435,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4499,10 +4492,10 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -4511,26 +4504,26 @@
         <v>73</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4542,15 +4535,17 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -4587,50 +4582,50 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>73</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>73</v>
@@ -4642,16 +4637,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4689,39 +4684,39 @@
         <v>73</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>156</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4729,7 +4724,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>79</v>
@@ -4744,17 +4739,15 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>73</v>
@@ -4803,10 +4796,10 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>79</v>
@@ -4815,15 +4808,15 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4846,13 +4839,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4903,7 +4896,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4915,15 +4908,15 @@
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5003,7 +4996,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -5015,106 +5008,6 @@
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-allergy-intolerance.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-allergy-intolerance.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-allergy-intolerance.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-allergy-intolerance.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -1931,13 +1935,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1988,7 +1992,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2005,10 +2009,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2031,13 +2035,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2088,7 +2092,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2105,10 +2109,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2131,13 +2135,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2188,7 +2192,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2205,10 +2209,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2231,13 +2235,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2288,7 +2292,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2305,10 +2309,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2331,13 +2335,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2388,7 +2392,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2405,10 +2409,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2431,13 +2435,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2488,7 +2492,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2505,10 +2509,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2531,13 +2535,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2567,10 +2571,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2588,7 +2592,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2605,10 +2609,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2631,13 +2635,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2667,7 +2671,7 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
         <v>73</v>
@@ -2688,7 +2692,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2705,10 +2709,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2731,13 +2735,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2788,7 +2792,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -2805,10 +2809,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2831,13 +2835,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2888,7 +2892,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2905,10 +2909,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2931,13 +2935,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2967,10 +2971,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2988,7 +2992,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -3005,10 +3009,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3031,13 +3035,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3067,10 +3071,10 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -3088,7 +3092,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -3105,10 +3109,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3131,13 +3135,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3167,10 +3171,10 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3188,7 +3192,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3205,10 +3209,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3231,13 +3235,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3288,7 +3292,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3300,15 +3304,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3331,13 +3335,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3388,7 +3392,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3405,14 +3409,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3431,16 +3435,16 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3478,19 +3482,19 @@
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3502,15 +3506,15 @@
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3533,16 +3537,16 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3592,7 +3596,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3609,10 +3613,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3635,13 +3639,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3692,7 +3696,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3704,15 +3708,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3735,13 +3739,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3792,7 +3796,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3809,10 +3813,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3835,13 +3839,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3892,7 +3896,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3909,10 +3913,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3938,10 +3942,10 @@
         <v>80</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3992,7 +3996,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -4009,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4035,13 +4039,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4071,7 +4075,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4092,7 +4096,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4109,10 +4113,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4135,13 +4139,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4171,7 +4175,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4192,7 +4196,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -4209,10 +4213,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4235,13 +4239,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4271,10 +4275,10 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4292,7 +4296,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4309,10 +4313,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4335,13 +4339,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4392,7 +4396,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4404,15 +4408,15 @@
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4435,13 +4439,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4492,7 +4496,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4509,14 +4513,14 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -4535,16 +4539,16 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4582,19 +4586,19 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4606,15 +4610,15 @@
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4637,16 +4641,16 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4696,7 +4700,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -4713,10 +4717,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4739,13 +4743,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4796,7 +4800,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4808,15 +4812,15 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4839,13 +4843,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4896,7 +4900,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4913,10 +4917,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4939,13 +4943,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4996,7 +5000,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="219">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-allergy-intolerance.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-allergy-intolerance.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-allergy-intolerance.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-allergy-intolerance.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-allergy-intolerance.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.header.source</t>
+    <t>fr-lm-allergy-intolerance.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-allergy-intolerance.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -454,7 +496,7 @@
     <t>commentaire</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.status</t>
+    <t>fr-lm-allergy-intolerance.clinicalStatus</t>
   </si>
   <si>
     <t>Statut clinique de l'allergie</t>
@@ -957,11 +999,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.61328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.61328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.32421875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.32421875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -991,7 +1033,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.06640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="45.68359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -1735,13 +1777,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1792,7 +1834,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1809,10 +1851,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1835,13 +1877,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1892,7 +1934,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1909,10 +1951,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1935,13 +1977,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1992,7 +2034,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -2009,10 +2051,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2035,7 +2077,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2135,13 +2177,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2192,7 +2234,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2209,10 +2251,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2223,7 +2265,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2235,13 +2277,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2292,13 +2334,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2309,10 +2351,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2323,7 +2365,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2335,13 +2377,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2392,13 +2434,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2409,10 +2451,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2423,7 +2465,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2435,13 +2477,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2492,13 +2534,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2509,10 +2551,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2520,7 +2562,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2535,13 +2577,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2571,10 +2613,10 @@
         <v>73</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>73</v>
@@ -2592,10 +2634,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2609,10 +2651,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2635,13 +2677,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2671,11 +2713,11 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="Z17" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
       </c>
@@ -2692,7 +2734,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2709,10 +2751,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2720,7 +2762,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -2735,13 +2777,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2792,10 +2834,10 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>79</v>
@@ -2809,10 +2851,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2835,13 +2877,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2892,7 +2934,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2909,10 +2951,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2920,7 +2962,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2935,13 +2977,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2971,31 +3013,31 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="Z20" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -3009,10 +3051,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3020,7 +3062,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -3035,13 +3077,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3071,31 +3113,31 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="Z21" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>144</v>
-      </c>
       <c r="AG21" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -3109,10 +3151,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3120,7 +3162,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3135,13 +3177,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3171,10 +3213,10 @@
         <v>73</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3192,10 +3234,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3209,10 +3251,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3220,7 +3262,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3235,13 +3277,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>154</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3292,10 +3334,10 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>79</v>
@@ -3304,15 +3346,15 @@
         <v>73</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3335,13 +3377,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3371,10 +3413,10 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -3392,7 +3434,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3409,21 +3451,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3435,17 +3477,15 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>73</v>
@@ -3473,48 +3513,48 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>161</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3522,7 +3562,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3537,17 +3577,15 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>73</v>
@@ -3575,10 +3613,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3596,10 +3634,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3613,10 +3651,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3624,7 +3662,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3639,13 +3677,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3696,10 +3734,10 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3708,15 +3746,15 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3739,13 +3777,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3796,7 +3834,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3813,21 +3851,21 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3839,15 +3877,17 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>73</v>
@@ -3884,39 +3924,39 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>73</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3924,10 +3964,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>73</v>
@@ -3939,15 +3979,17 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>80</v>
+        <v>185</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M30" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N30" s="2"/>
+      <c r="N30" t="s" s="2">
+        <v>188</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -3996,13 +4038,13 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>73</v>
@@ -4013,10 +4055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4039,13 +4081,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4075,7 +4117,7 @@
         <v>73</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>190</v>
+        <v>73</v>
       </c>
       <c r="Z31" t="s" s="2">
         <v>73</v>
@@ -4096,7 +4138,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4108,15 +4150,15 @@
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>73</v>
+        <v>195</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4124,7 +4166,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4139,13 +4181,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4175,7 +4217,7 @@
         <v>73</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>193</v>
+        <v>73</v>
       </c>
       <c r="Z32" t="s" s="2">
         <v>73</v>
@@ -4196,10 +4238,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4213,10 +4255,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4239,13 +4281,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4275,10 +4317,10 @@
         <v>73</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>73</v>
@@ -4296,7 +4338,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4313,10 +4355,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4324,10 +4366,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4339,13 +4381,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4396,27 +4438,27 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4439,13 +4481,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4475,7 +4517,7 @@
         <v>73</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>73</v>
+        <v>204</v>
       </c>
       <c r="Z35" t="s" s="2">
         <v>73</v>
@@ -4496,7 +4538,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4513,21 +4555,21 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>73</v>
@@ -4539,17 +4581,15 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>163</v>
+        <v>206</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>73</v>
@@ -4577,7 +4617,7 @@
         <v>73</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="Z36" t="s" s="2">
         <v>73</v>
@@ -4586,39 +4626,39 @@
         <v>73</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>166</v>
+        <v>73</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>167</v>
+        <v>73</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>169</v>
+        <v>205</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4626,7 +4666,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>79</v>
@@ -4641,17 +4681,15 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>73</v>
@@ -4679,10 +4717,10 @@
         <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>73</v>
+        <v>210</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>73</v>
+        <v>211</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -4700,10 +4738,10 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -4717,10 +4755,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4728,7 +4766,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>79</v>
@@ -4743,13 +4781,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4800,10 +4838,10 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>79</v>
@@ -4812,15 +4850,15 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>181</v>
+        <v>169</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4843,13 +4881,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4900,7 +4938,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4917,21 +4955,21 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -4943,15 +4981,17 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>73</v>
@@ -4988,30 +5028,432 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>73</v>
+        <v>181</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
